--- a/PICK_N_PLACE/JLCSMT_Sample_CPL1.xlsx
+++ b/PICK_N_PLACE/JLCSMT_Sample_CPL1.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="340">
   <si>
     <t xml:space="preserve">Designator</t>
   </si>
@@ -994,6 +994,12 @@
     <t xml:space="preserve">TP79</t>
   </si>
   <si>
+    <t xml:space="preserve">PS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PS3</t>
+  </si>
+  <si>
     <t xml:space="preserve">U2</t>
   </si>
   <si>
@@ -1010,6 +1016,9 @@
   </si>
   <si>
     <t xml:space="preserve">U10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U12</t>
   </si>
   <si>
     <t xml:space="preserve">U11</t>
@@ -1153,7 +1162,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E331"/>
+  <dimension ref="A1:E335"/>
   <sheetFormatPr defaultColWidth="8.89453125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.56"/>
@@ -6574,16 +6583,16 @@
         <v>324</v>
       </c>
       <c r="B319" s="0" t="n">
-        <v>112</v>
+        <v>75.923102</v>
       </c>
       <c r="C319" s="0" t="n">
-        <v>-74.5</v>
+        <v>-75.761934</v>
       </c>
       <c r="D319" s="0" t="s">
-        <v>165</v>
+        <v>6</v>
       </c>
       <c r="E319" s="0" t="n">
-        <v>135</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="320" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6591,16 +6600,16 @@
         <v>325</v>
       </c>
       <c r="B320" s="0" t="n">
-        <v>112.33</v>
+        <v>76.263102</v>
       </c>
       <c r="C320" s="0" t="n">
-        <v>-64.24</v>
+        <v>-62.721934</v>
       </c>
       <c r="D320" s="0" t="s">
-        <v>165</v>
+        <v>6</v>
       </c>
       <c r="E320" s="0" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="321" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6608,16 +6617,16 @@
         <v>326</v>
       </c>
       <c r="B321" s="0" t="n">
-        <v>112.997352</v>
+        <v>112</v>
       </c>
       <c r="C321" s="0" t="n">
-        <v>-97.384433</v>
+        <v>-74.5</v>
       </c>
       <c r="D321" s="0" t="s">
         <v>165</v>
       </c>
       <c r="E321" s="0" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6625,16 +6634,16 @@
         <v>327</v>
       </c>
       <c r="B322" s="0" t="n">
-        <v>89.193652</v>
+        <v>112.33</v>
       </c>
       <c r="C322" s="0" t="n">
-        <v>-110.205</v>
+        <v>-64.24</v>
       </c>
       <c r="D322" s="0" t="s">
         <v>165</v>
       </c>
       <c r="E322" s="0" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="323" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6642,10 +6651,10 @@
         <v>328</v>
       </c>
       <c r="B323" s="0" t="n">
-        <v>136.671348</v>
+        <v>112.997352</v>
       </c>
       <c r="C323" s="0" t="n">
-        <v>-109.735</v>
+        <v>-97.384433</v>
       </c>
       <c r="D323" s="0" t="s">
         <v>165</v>
@@ -6656,47 +6665,47 @@
     </row>
     <row r="324" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="0" t="s">
-        <v>329</v>
+        <v>158</v>
       </c>
       <c r="B324" s="0" t="n">
-        <v>90.31</v>
+        <v>85.72</v>
       </c>
       <c r="C324" s="0" t="n">
-        <v>-86.871348</v>
+        <v>-85.875</v>
       </c>
       <c r="D324" s="0" t="s">
-        <v>165</v>
+        <v>6</v>
       </c>
       <c r="E324" s="0" t="n">
-        <v>65</v>
+        <v>180</v>
       </c>
     </row>
     <row r="325" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="0" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B325" s="0" t="n">
-        <v>135.250919</v>
+        <v>89.193652</v>
       </c>
       <c r="C325" s="0" t="n">
-        <v>-87.246896</v>
+        <v>-110.205</v>
       </c>
       <c r="D325" s="0" t="s">
         <v>165</v>
       </c>
       <c r="E325" s="0" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="0" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B326" s="0" t="n">
-        <v>120.5</v>
+        <v>136.671348</v>
       </c>
       <c r="C326" s="0" t="n">
-        <v>-120.825</v>
+        <v>-109.735</v>
       </c>
       <c r="D326" s="0" t="s">
         <v>165</v>
@@ -6707,86 +6716,154 @@
     </row>
     <row r="327" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="0" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B327" s="0" t="n">
-        <v>81.25</v>
+        <v>90.31</v>
       </c>
       <c r="C327" s="0" t="n">
-        <v>-128.95</v>
+        <v>-86.871348</v>
       </c>
       <c r="D327" s="0" t="s">
         <v>165</v>
       </c>
       <c r="E327" s="0" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="0" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B328" s="0" t="n">
-        <v>108.75</v>
+        <v>87.053102</v>
       </c>
       <c r="C328" s="0" t="n">
-        <v>-108.349999</v>
+        <v>-66.846934</v>
       </c>
       <c r="D328" s="0" t="s">
-        <v>165</v>
+        <v>6</v>
       </c>
       <c r="E328" s="0" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="0" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B329" s="0" t="n">
-        <v>70.0174</v>
+        <v>135.250919</v>
       </c>
       <c r="C329" s="0" t="n">
-        <v>-129.80005</v>
+        <v>-87.246896</v>
       </c>
       <c r="D329" s="0" t="s">
         <v>165</v>
       </c>
       <c r="E329" s="0" t="n">
-        <v>90</v>
+        <v>115</v>
       </c>
     </row>
     <row r="330" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="0" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B330" s="0" t="n">
-        <v>92</v>
+        <v>120.5</v>
       </c>
       <c r="C330" s="0" t="n">
-        <v>-130.6</v>
+        <v>-120.825</v>
       </c>
       <c r="D330" s="0" t="s">
         <v>165</v>
       </c>
       <c r="E330" s="0" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="0" t="s">
+        <v>335</v>
+      </c>
+      <c r="B331" s="0" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="C331" s="0" t="n">
+        <v>-128.95</v>
+      </c>
+      <c r="D331" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="E331" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A332" s="0" t="s">
         <v>336</v>
       </c>
-      <c r="B331" s="0" t="n">
+      <c r="B332" s="0" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="C332" s="0" t="n">
+        <v>-108.349999</v>
+      </c>
+      <c r="D332" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="E332" s="0" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="333" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A333" s="0" t="s">
+        <v>337</v>
+      </c>
+      <c r="B333" s="0" t="n">
+        <v>70.0174</v>
+      </c>
+      <c r="C333" s="0" t="n">
+        <v>-129.80005</v>
+      </c>
+      <c r="D333" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="E333" s="0" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="334" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A334" s="0" t="s">
+        <v>338</v>
+      </c>
+      <c r="B334" s="0" t="n">
+        <v>92</v>
+      </c>
+      <c r="C334" s="0" t="n">
+        <v>-130.6</v>
+      </c>
+      <c r="D334" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="E334" s="0" t="n">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="335" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A335" s="0" t="s">
+        <v>339</v>
+      </c>
+      <c r="B335" s="0" t="n">
         <v>126</v>
       </c>
-      <c r="C331" s="0" t="n">
+      <c r="C335" s="0" t="n">
         <v>-94.65</v>
       </c>
-      <c r="D331" s="0" t="s">
-        <v>165</v>
-      </c>
-      <c r="E331" s="0" t="n">
+      <c r="D335" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="E335" s="0" t="n">
         <v>90</v>
       </c>
     </row>
